--- a/Dowling/dowling-vs-crk-offense.xlsx
+++ b/Dowling/dowling-vs-crk-offense.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R86ec2fe42d39477e"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R00577a3c3fc34b69"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -254,6 +266,9 @@
   </si>
   <si>
     <t>MONEY</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
   <si>
     <t>Q STORM</t>
@@ -299,7 +314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y129"/>
+  <dimension ref="A1:AC129"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -377,6 +392,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -386,7 +413,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -395,13 +422,13 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +439,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -421,13 +448,13 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -438,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -447,13 +474,13 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +491,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -473,13 +500,13 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -490,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -499,13 +526,13 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +543,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -528,25 +555,25 @@
         <v>-40</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="S7" t="s">
-        <v>38</v>
-      </c>
-      <c r="T7" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="X7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -557,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -569,25 +596,28 @@
         <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8" t="s">
         <v>41</v>
       </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S8" t="s">
-        <v>42</v>
-      </c>
-      <c r="T8" t="s">
-        <v>43</v>
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -598,37 +628,37 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
         <v>36</v>
       </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="S9" t="s">
-        <v>38</v>
-      </c>
-      <c r="T9" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="X9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -639,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -651,25 +681,25 @@
         <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
-      </c>
-      <c r="S10" t="s">
-        <v>46</v>
-      </c>
-      <c r="T10" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="X10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -680,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -692,25 +722,28 @@
         <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>37</v>
-      </c>
-      <c r="S11" t="s">
-        <v>42</v>
-      </c>
-      <c r="T11" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="P11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -721,7 +754,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -733,25 +766,25 @@
         <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J12">
         <v>38</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
-      </c>
-      <c r="S12" t="s">
-        <v>38</v>
-      </c>
-      <c r="T12" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="X12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -762,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -774,13 +807,13 @@
         <v>-2</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -791,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -800,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -817,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -826,13 +859,13 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -843,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -852,7 +885,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -863,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -872,13 +905,13 @@
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I17" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -889,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -898,13 +931,13 @@
         <v>7</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -915,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -924,13 +957,13 @@
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +974,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -950,13 +983,13 @@
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
@@ -967,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -976,13 +1009,13 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -993,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1005,27 +1038,27 @@
         <v>50</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>44</v>
-      </c>
-      <c r="S22" t="s">
-        <v>55</v>
-      </c>
-      <c r="T22" t="s">
-        <v>56</v>
-      </c>
-      <c r="X22">
+        <v>48</v>
+      </c>
+      <c r="X22" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1037,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1049,27 +1082,27 @@
         <v>50</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J23">
         <v>-6</v>
       </c>
       <c r="K23" t="s">
-        <v>44</v>
-      </c>
-      <c r="S23" t="s">
-        <v>58</v>
-      </c>
-      <c r="T23" t="s">
-        <v>59</v>
-      </c>
-      <c r="X23">
+        <v>48</v>
+      </c>
+      <c r="X23" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1081,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1093,27 +1126,27 @@
         <v>-44</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I24" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>44</v>
-      </c>
-      <c r="S24" t="s">
-        <v>61</v>
-      </c>
-      <c r="T24" t="s">
-        <v>62</v>
-      </c>
-      <c r="X24">
+        <v>48</v>
+      </c>
+      <c r="X24" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1125,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1137,25 +1170,25 @@
         <v>-45</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J25">
         <v>12</v>
       </c>
       <c r="K25" t="s">
-        <v>37</v>
-      </c>
-      <c r="S25" t="s">
-        <v>63</v>
-      </c>
-      <c r="T25" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="X25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -1166,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -1178,27 +1211,27 @@
         <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26" t="s">
         <v>41</v>
       </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26" t="s">
-        <v>37</v>
-      </c>
-      <c r="S26" t="s">
-        <v>38</v>
-      </c>
-      <c r="T26" t="s">
-        <v>50</v>
-      </c>
-      <c r="X26">
+      <c r="X26" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1210,42 +1243,42 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>40</v>
+      </c>
+      <c r="G27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
         <v>36</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>10</v>
-      </c>
-      <c r="F27">
-        <v>40</v>
-      </c>
-      <c r="G27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" t="s">
-        <v>32</v>
       </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27" t="s">
-        <v>37</v>
-      </c>
-      <c r="S27" t="s">
-        <v>46</v>
-      </c>
-      <c r="T27" t="s">
-        <v>45</v>
-      </c>
-      <c r="V27" t="s">
-        <v>26</v>
-      </c>
-      <c r="X27">
+        <v>41</v>
+      </c>
+      <c r="X27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1257,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1269,30 +1302,30 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I28" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J28">
         <v>16</v>
       </c>
       <c r="K28" t="s">
-        <v>37</v>
-      </c>
-      <c r="S28" t="s">
-        <v>38</v>
-      </c>
-      <c r="T28" t="s">
-        <v>64</v>
-      </c>
-      <c r="V28" t="s">
-        <v>30</v>
-      </c>
-      <c r="X28">
+        <v>41</v>
+      </c>
+      <c r="X28" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1304,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1316,25 +1349,25 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I29" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J29">
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>37</v>
-      </c>
-      <c r="S29" t="s">
-        <v>38</v>
-      </c>
-      <c r="T29" t="s">
-        <v>65</v>
+        <v>41</v>
+      </c>
+      <c r="X29" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -1345,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1357,25 +1390,25 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>44</v>
-      </c>
-      <c r="S30" t="s">
-        <v>58</v>
-      </c>
-      <c r="T30" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="X30" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31">
@@ -1386,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -1398,13 +1431,13 @@
         <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="S31" t="s">
-        <v>38</v>
+      <c r="X31" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="32">
@@ -1415,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1427,25 +1460,25 @@
         <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H32" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I32" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>44</v>
-      </c>
-      <c r="S32" t="s">
-        <v>38</v>
-      </c>
-      <c r="T32" t="s">
-        <v>66</v>
+        <v>48</v>
+      </c>
+      <c r="X32" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="33">
@@ -1456,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1468,25 +1501,25 @@
         <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
       <c r="K33" t="s">
-        <v>37</v>
-      </c>
-      <c r="S33" t="s">
-        <v>38</v>
-      </c>
-      <c r="T33" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="X33" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="34">
@@ -1497,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1509,10 +1542,10 @@
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
@@ -1523,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1532,13 +1565,13 @@
         <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
@@ -1549,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1558,13 +1591,13 @@
         <v>10</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I36" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
@@ -1575,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1584,13 +1617,13 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -1601,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1610,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H38" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I38" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -1627,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1636,13 +1669,13 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -1653,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1662,13 +1695,13 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I40" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41">
@@ -1679,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -1688,13 +1721,13 @@
         <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
@@ -1705,7 +1738,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1714,13 +1747,13 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I42" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -1731,7 +1764,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1743,25 +1776,25 @@
         <v>-20</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I43" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43">
+        <v>35</v>
+      </c>
+      <c r="K43" t="s">
         <v>41</v>
       </c>
-      <c r="J43">
-        <v>35</v>
-      </c>
-      <c r="K43" t="s">
-        <v>37</v>
-      </c>
-      <c r="S43" t="s">
-        <v>38</v>
-      </c>
-      <c r="T43" t="s">
-        <v>68</v>
+      <c r="X43" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="44">
@@ -1772,7 +1805,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1784,25 +1817,25 @@
         <v>45</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H44" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I44" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J44">
         <v>6</v>
       </c>
       <c r="K44" t="s">
-        <v>37</v>
-      </c>
-      <c r="S44" t="s">
-        <v>69</v>
-      </c>
-      <c r="T44" t="s">
-        <v>69</v>
+        <v>41</v>
+      </c>
+      <c r="X44" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="45">
@@ -1813,7 +1846,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1825,27 +1858,27 @@
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45" t="s">
-        <v>37</v>
-      </c>
-      <c r="S45" t="s">
-        <v>38</v>
-      </c>
-      <c r="T45" t="s">
-        <v>70</v>
-      </c>
-      <c r="X45">
+        <v>41</v>
+      </c>
+      <c r="X45" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB45">
         <v>4</v>
       </c>
     </row>
@@ -1857,7 +1890,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1869,21 +1902,21 @@
         <v>34</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J46">
         <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>37</v>
-      </c>
-      <c r="S46" t="s">
-        <v>38</v>
-      </c>
-      <c r="X46">
+        <v>41</v>
+      </c>
+      <c r="X46" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -1895,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1907,27 +1940,27 @@
         <v>29</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H47" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J47">
         <v>5</v>
       </c>
       <c r="K47" t="s">
-        <v>37</v>
-      </c>
-      <c r="S47" t="s">
-        <v>38</v>
-      </c>
-      <c r="T47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X47">
+        <v>41</v>
+      </c>
+      <c r="X47" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB47">
         <v>4</v>
       </c>
     </row>
@@ -1939,7 +1972,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1951,25 +1984,25 @@
         <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I48" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J48">
         <v>5</v>
       </c>
       <c r="K48" t="s">
-        <v>37</v>
-      </c>
-      <c r="S48" t="s">
-        <v>72</v>
-      </c>
-      <c r="T48" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="X48" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="49">
@@ -1980,7 +2013,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1992,25 +2025,25 @@
         <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J49">
         <v>-2</v>
       </c>
       <c r="K49" t="s">
-        <v>44</v>
-      </c>
-      <c r="S49" t="s">
-        <v>58</v>
-      </c>
-      <c r="T49" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="X49" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="50">
@@ -2021,7 +2054,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2033,25 +2066,25 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I50" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J50">
         <v>12</v>
       </c>
       <c r="K50" t="s">
-        <v>37</v>
-      </c>
-      <c r="S50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T50" t="s">
-        <v>73</v>
+        <v>41</v>
+      </c>
+      <c r="X50" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="51">
@@ -2062,7 +2095,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2074,25 +2107,25 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I51" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J51">
         <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>37</v>
-      </c>
-      <c r="S51" t="s">
-        <v>69</v>
-      </c>
-      <c r="T51" t="s">
-        <v>69</v>
+        <v>41</v>
+      </c>
+      <c r="X51" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="52">
@@ -2103,7 +2136,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2115,16 +2148,16 @@
         <v>3</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I52" t="s">
-        <v>52</v>
-      </c>
-      <c r="T52" t="s">
-        <v>76</v>
+        <v>56</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="53">
@@ -2135,7 +2168,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2144,13 +2177,13 @@
         <v>10</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
@@ -2161,7 +2194,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2170,13 +2203,13 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
@@ -2187,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2196,13 +2229,13 @@
         <v>7</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I55" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -2213,7 +2246,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2222,13 +2255,13 @@
         <v>10</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H56" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I56" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -2239,7 +2272,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2248,13 +2281,13 @@
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I57" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58">
@@ -2265,7 +2298,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -2274,13 +2307,13 @@
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I58" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59">
@@ -2291,7 +2324,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2300,18 +2333,18 @@
         <v>4</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I59" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s">
-        <v>37</v>
-      </c>
-      <c r="X59">
+        <v>41</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -2323,7 +2356,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2335,27 +2368,27 @@
         <v>42</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I60" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J60">
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>37</v>
-      </c>
-      <c r="S60" t="s">
-        <v>72</v>
-      </c>
-      <c r="T60" t="s">
-        <v>78</v>
-      </c>
-      <c r="X60">
+        <v>41</v>
+      </c>
+      <c r="X60" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -2367,7 +2400,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2379,27 +2412,27 @@
         <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J61">
         <v>12</v>
       </c>
       <c r="K61" t="s">
-        <v>37</v>
-      </c>
-      <c r="S61" t="s">
-        <v>38</v>
-      </c>
-      <c r="T61" t="s">
-        <v>50</v>
-      </c>
-      <c r="X61">
+        <v>41</v>
+      </c>
+      <c r="X61" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -2411,7 +2444,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2423,25 +2456,25 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J62">
         <v>14</v>
       </c>
       <c r="K62" t="s">
-        <v>37</v>
-      </c>
-      <c r="S62" t="s">
-        <v>46</v>
-      </c>
-      <c r="T62" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="X62" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="63">
@@ -2452,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2464,19 +2497,19 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H63" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s">
-        <v>44</v>
-      </c>
-      <c r="T63" t="s">
-        <v>80</v>
+        <v>48</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="64">
@@ -2487,7 +2520,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2496,13 +2529,13 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -2513,7 +2546,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -2522,13 +2555,13 @@
         <v>6</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I65" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
@@ -2539,7 +2572,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -2548,13 +2581,13 @@
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H66" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I66" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67">
@@ -2565,7 +2598,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>4</v>
@@ -2574,13 +2607,13 @@
         <v>3</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H67" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I67" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68">
@@ -2591,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2603,25 +2636,28 @@
         <v>35</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H68" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I68" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J68">
         <v>11</v>
       </c>
       <c r="K68" t="s">
-        <v>37</v>
-      </c>
-      <c r="S68" t="s">
-        <v>42</v>
-      </c>
-      <c r="T68" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="P68" t="s">
+        <v>29</v>
+      </c>
+      <c r="X68" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="69">
@@ -2632,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2644,25 +2680,25 @@
         <v>24</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H69" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I69" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J69">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>44</v>
-      </c>
-      <c r="S69" t="s">
-        <v>69</v>
-      </c>
-      <c r="T69" t="s">
-        <v>69</v>
+        <v>48</v>
+      </c>
+      <c r="X69" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="70">
@@ -2673,7 +2709,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -2685,25 +2721,28 @@
         <v>23</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J70">
         <v>4</v>
       </c>
       <c r="K70" t="s">
-        <v>44</v>
-      </c>
-      <c r="S70" t="s">
-        <v>42</v>
-      </c>
-      <c r="T70" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="P70" t="s">
+        <v>29</v>
+      </c>
+      <c r="X70" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -2714,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -2726,25 +2765,28 @@
         <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H71" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J71">
         <v>4</v>
       </c>
       <c r="K71" t="s">
-        <v>44</v>
-      </c>
-      <c r="S71" t="s">
-        <v>42</v>
-      </c>
-      <c r="T71" t="s">
-        <v>81</v>
+        <v>48</v>
+      </c>
+      <c r="P71" t="s">
+        <v>85</v>
+      </c>
+      <c r="X71" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="72">
@@ -2755,7 +2797,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -2767,25 +2809,25 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H72" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J72">
         <v>5</v>
       </c>
       <c r="K72" t="s">
-        <v>37</v>
-      </c>
-      <c r="S72" t="s">
-        <v>38</v>
-      </c>
-      <c r="T72" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="X72" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="73">
@@ -2796,7 +2838,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2808,25 +2850,28 @@
         <v>10</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I73" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J73">
         <v>5</v>
       </c>
       <c r="K73" t="s">
-        <v>37</v>
-      </c>
-      <c r="S73" t="s">
-        <v>42</v>
-      </c>
-      <c r="T73" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="P73" t="s">
+        <v>29</v>
+      </c>
+      <c r="X73" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="74">
@@ -2837,7 +2882,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -2849,25 +2894,25 @@
         <v>5</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J74">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>44</v>
-      </c>
-      <c r="S74" t="s">
-        <v>46</v>
-      </c>
-      <c r="T74" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="X74" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="75">
@@ -2878,7 +2923,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -2890,25 +2935,25 @@
         <v>4</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
+        <v>53</v>
+      </c>
+      <c r="J75">
+        <v>4</v>
+      </c>
+      <c r="K75" t="s">
+        <v>41</v>
+      </c>
+      <c r="X75" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y75" t="s">
         <v>49</v>
-      </c>
-      <c r="J75">
-        <v>4</v>
-      </c>
-      <c r="K75" t="s">
-        <v>37</v>
-      </c>
-      <c r="S75" t="s">
-        <v>82</v>
-      </c>
-      <c r="T75" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="76">
@@ -2919,7 +2964,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2931,13 +2976,13 @@
         <v>3</v>
       </c>
       <c r="G76" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H76" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I76" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77">
@@ -2948,7 +2993,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2957,13 +3002,13 @@
         <v>10</v>
       </c>
       <c r="G77" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
@@ -2974,7 +3019,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2983,13 +3028,13 @@
         <v>10</v>
       </c>
       <c r="G78" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H78" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79">
@@ -3000,7 +3045,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -3009,13 +3054,13 @@
         <v>13</v>
       </c>
       <c r="G79" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H79" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I79" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80">
@@ -3026,7 +3071,7 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3035,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81">
@@ -3046,7 +3091,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3055,13 +3100,13 @@
         <v>10</v>
       </c>
       <c r="G81" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H81" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I81" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82">
@@ -3072,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3081,13 +3126,13 @@
         <v>10</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H82" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I82" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83">
@@ -3098,7 +3143,7 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -3107,13 +3152,13 @@
         <v>10</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H83" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84">
@@ -3124,7 +3169,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3136,25 +3181,25 @@
         <v>-17</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H84" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J84">
         <v>8</v>
       </c>
       <c r="K84" t="s">
-        <v>37</v>
-      </c>
-      <c r="S84" t="s">
-        <v>38</v>
-      </c>
-      <c r="T84" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="X84" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="85">
@@ -3165,7 +3210,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -3177,25 +3222,25 @@
         <v>-25</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J85">
         <v>-3</v>
       </c>
       <c r="K85" t="s">
-        <v>44</v>
-      </c>
-      <c r="S85" t="s">
-        <v>38</v>
-      </c>
-      <c r="T85" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="X85" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="86">
@@ -3206,7 +3251,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -3218,25 +3263,25 @@
         <v>-22</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H86" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I86" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J86">
         <v>13</v>
       </c>
       <c r="K86" t="s">
-        <v>37</v>
-      </c>
-      <c r="S86" t="s">
-        <v>55</v>
-      </c>
-      <c r="T86" t="s">
-        <v>84</v>
+        <v>41</v>
+      </c>
+      <c r="X86" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="87">
@@ -3247,7 +3292,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3259,25 +3304,25 @@
         <v>-35</v>
       </c>
       <c r="G87" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H87" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I87" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J87">
         <v>-1</v>
       </c>
       <c r="K87" t="s">
-        <v>44</v>
-      </c>
-      <c r="S87" t="s">
-        <v>46</v>
-      </c>
-      <c r="T87" t="s">
-        <v>85</v>
+        <v>48</v>
+      </c>
+      <c r="X87" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="88">
@@ -3288,7 +3333,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -3300,25 +3345,28 @@
         <v>-34</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J88">
         <v>16</v>
       </c>
       <c r="K88" t="s">
-        <v>37</v>
-      </c>
-      <c r="S88" t="s">
-        <v>42</v>
-      </c>
-      <c r="T88" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="P88" t="s">
+        <v>29</v>
+      </c>
+      <c r="X88" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="89">
@@ -3329,7 +3377,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3341,25 +3389,25 @@
         <v>50</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J89">
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>44</v>
-      </c>
-      <c r="S89" t="s">
-        <v>46</v>
-      </c>
-      <c r="T89" t="s">
-        <v>86</v>
+        <v>48</v>
+      </c>
+      <c r="X89" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="90">
@@ -3370,7 +3418,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -3382,25 +3430,25 @@
         <v>48</v>
       </c>
       <c r="G90" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J90">
         <v>4</v>
       </c>
       <c r="K90" t="s">
-        <v>37</v>
-      </c>
-      <c r="S90" t="s">
-        <v>46</v>
-      </c>
-      <c r="T90" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="X90" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="91">
@@ -3411,7 +3459,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -3423,25 +3471,25 @@
         <v>44</v>
       </c>
       <c r="G91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H91" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I91" t="s">
+        <v>45</v>
+      </c>
+      <c r="J91">
+        <v>10</v>
+      </c>
+      <c r="K91" t="s">
         <v>41</v>
       </c>
-      <c r="J91">
-        <v>10</v>
-      </c>
-      <c r="K91" t="s">
-        <v>37</v>
-      </c>
-      <c r="S91" t="s">
-        <v>55</v>
-      </c>
-      <c r="T91" t="s">
-        <v>56</v>
+      <c r="X91" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="92">
@@ -3452,7 +3500,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3464,25 +3512,28 @@
         <v>34</v>
       </c>
       <c r="G92" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I92" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J92">
         <v>-1</v>
       </c>
       <c r="K92" t="s">
-        <v>44</v>
-      </c>
-      <c r="S92" t="s">
-        <v>42</v>
-      </c>
-      <c r="T92" t="s">
-        <v>87</v>
+        <v>48</v>
+      </c>
+      <c r="P92" t="s">
+        <v>29</v>
+      </c>
+      <c r="X92" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="93">
@@ -3493,7 +3544,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -3505,25 +3556,25 @@
         <v>35</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H93" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J93">
         <v>8</v>
       </c>
       <c r="K93" t="s">
-        <v>37</v>
-      </c>
-      <c r="S93" t="s">
-        <v>38</v>
-      </c>
-      <c r="T93" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="X93" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="94">
@@ -3534,7 +3585,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -3546,25 +3597,25 @@
         <v>27</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I94" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J94">
         <v>7</v>
       </c>
       <c r="K94" t="s">
-        <v>37</v>
-      </c>
-      <c r="S94" t="s">
-        <v>38</v>
-      </c>
-      <c r="T94" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="X94" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -3575,7 +3626,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3587,25 +3638,25 @@
         <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J95">
         <v>11</v>
       </c>
       <c r="K95" t="s">
-        <v>37</v>
-      </c>
-      <c r="S95" t="s">
-        <v>38</v>
-      </c>
-      <c r="T95" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="X95" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="96">
@@ -3616,7 +3667,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -3628,25 +3679,25 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J96">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>44</v>
-      </c>
-      <c r="S96" t="s">
-        <v>38</v>
-      </c>
-      <c r="T96" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="X96" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="97">
@@ -3657,7 +3708,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -3669,25 +3720,25 @@
         <v>8</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>-4</v>
       </c>
       <c r="K97" t="s">
-        <v>44</v>
-      </c>
-      <c r="S97" t="s">
-        <v>38</v>
-      </c>
-      <c r="T97" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="X97" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="98">
@@ -3698,7 +3749,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D98">
         <v>3</v>
@@ -3710,25 +3761,25 @@
         <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J98">
         <v>12</v>
       </c>
       <c r="K98" t="s">
-        <v>37</v>
-      </c>
-      <c r="S98" t="s">
-        <v>46</v>
-      </c>
-      <c r="T98" t="s">
-        <v>86</v>
+        <v>41</v>
+      </c>
+      <c r="X98" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="99">
@@ -3739,7 +3790,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3751,13 +3802,13 @@
         <v>3</v>
       </c>
       <c r="G99" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H99" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I99" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100">
@@ -3768,7 +3819,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3777,13 +3828,13 @@
         <v>10</v>
       </c>
       <c r="G100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H100" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I100" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101">
@@ -3794,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3803,13 +3854,13 @@
         <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102">
@@ -3820,7 +3871,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3829,13 +3880,13 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103">
@@ -3846,7 +3897,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3855,13 +3906,13 @@
         <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104">
@@ -3872,7 +3923,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -3881,13 +3932,13 @@
         <v>17</v>
       </c>
       <c r="G104" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H104" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I104" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105">
@@ -3898,7 +3949,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3907,13 +3958,13 @@
         <v>10</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I105" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106">
@@ -3924,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -3933,13 +3984,13 @@
         <v>10</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I106" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107">
@@ -3950,7 +4001,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -3959,13 +4010,13 @@
         <v>10</v>
       </c>
       <c r="G107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H107" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I107" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108">
@@ -3976,7 +4027,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D108">
         <v>4</v>
@@ -3985,15 +4036,15 @@
         <v>10</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I108" t="s">
-        <v>88</v>
-      </c>
-      <c r="X108">
+        <v>93</v>
+      </c>
+      <c r="AB108">
         <v>7</v>
       </c>
     </row>
@@ -4005,7 +4056,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -4014,27 +4065,27 @@
         <v>10</v>
       </c>
       <c r="G109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H109" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I109" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>44</v>
-      </c>
-      <c r="S109" t="s">
-        <v>46</v>
-      </c>
-      <c r="T109" t="s">
-        <v>64</v>
-      </c>
-      <c r="X109">
+        <v>48</v>
+      </c>
+      <c r="X109" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB109">
         <v>7</v>
       </c>
     </row>
@@ -4046,30 +4097,30 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
+        <v>40</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+      <c r="E110">
+        <v>10</v>
+      </c>
+      <c r="G110" t="s">
+        <v>34</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110" t="s">
         <v>36</v>
       </c>
-      <c r="D110">
-        <v>2</v>
-      </c>
-      <c r="E110">
-        <v>10</v>
-      </c>
-      <c r="G110" t="s">
-        <v>30</v>
-      </c>
-      <c r="H110" t="s">
-        <v>31</v>
-      </c>
-      <c r="I110" t="s">
-        <v>32</v>
-      </c>
-      <c r="S110" t="s">
-        <v>38</v>
-      </c>
-      <c r="T110" t="s">
-        <v>71</v>
-      </c>
-      <c r="X110">
+      <c r="X110" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB110">
         <v>7</v>
       </c>
     </row>
@@ -4081,7 +4132,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D111">
         <v>3</v>
@@ -4090,19 +4141,19 @@
         <v>7</v>
       </c>
       <c r="G111" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H111" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I111" t="s">
-        <v>54</v>
-      </c>
-      <c r="S111" t="s">
-        <v>46</v>
-      </c>
-      <c r="T111" t="s">
-        <v>85</v>
+        <v>58</v>
+      </c>
+      <c r="X111" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="112">
@@ -4113,7 +4164,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D112">
         <v>4</v>
@@ -4122,13 +4173,13 @@
         <v>7</v>
       </c>
       <c r="G112" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H112" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I112" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113">
@@ -4139,7 +4190,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4148,13 +4199,13 @@
         <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I113" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="114">
@@ -4165,7 +4216,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4174,13 +4225,13 @@
         <v>10</v>
       </c>
       <c r="G114" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H114" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I114" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115">
@@ -4191,7 +4242,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -4200,13 +4251,13 @@
         <v>29</v>
       </c>
       <c r="G115" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H115" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I115" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116">
@@ -4217,7 +4268,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -4226,13 +4277,13 @@
         <v>29</v>
       </c>
       <c r="G116" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H116" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I116" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117">
@@ -4243,7 +4294,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -4252,13 +4303,13 @@
         <v>29</v>
       </c>
       <c r="G117" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H117" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I117" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="118">
@@ -4269,7 +4320,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4278,19 +4329,19 @@
         <v>10</v>
       </c>
       <c r="G118" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H118" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I118" t="s">
-        <v>60</v>
-      </c>
-      <c r="S118" t="s">
-        <v>46</v>
-      </c>
-      <c r="T118" t="s">
-        <v>90</v>
+        <v>64</v>
+      </c>
+      <c r="X118" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="119">
@@ -4301,28 +4352,28 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119">
+        <v>2</v>
+      </c>
+      <c r="E119">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>30</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119" t="s">
         <v>36</v>
       </c>
-      <c r="D119">
-        <v>2</v>
-      </c>
-      <c r="E119">
-        <v>10</v>
-      </c>
-      <c r="G119" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" t="s">
-        <v>31</v>
-      </c>
-      <c r="I119" t="s">
-        <v>32</v>
-      </c>
-      <c r="S119" t="s">
-        <v>38</v>
-      </c>
-      <c r="T119" t="s">
-        <v>91</v>
+      <c r="X119" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="120">
@@ -4333,7 +4384,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -4342,19 +4393,19 @@
         <v>5</v>
       </c>
       <c r="G120" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S120" t="s">
-        <v>38</v>
-      </c>
-      <c r="T120" t="s">
-        <v>91</v>
+        <v>36</v>
+      </c>
+      <c r="X120" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="121">
@@ -4365,28 +4416,28 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
+        <v>40</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>10</v>
+      </c>
+      <c r="G121" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121" t="s">
         <v>36</v>
       </c>
-      <c r="D121">
-        <v>1</v>
-      </c>
-      <c r="E121">
-        <v>10</v>
-      </c>
-      <c r="G121" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" t="s">
-        <v>31</v>
-      </c>
-      <c r="I121" t="s">
-        <v>32</v>
-      </c>
-      <c r="S121" t="s">
-        <v>38</v>
-      </c>
-      <c r="T121" t="s">
-        <v>86</v>
+      <c r="X121" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="122">
@@ -4397,7 +4448,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -4406,19 +4457,19 @@
         <v>8</v>
       </c>
       <c r="G122" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
-      </c>
-      <c r="S122" t="s">
-        <v>46</v>
-      </c>
-      <c r="T122" t="s">
-        <v>91</v>
+        <v>36</v>
+      </c>
+      <c r="X122" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="123">
@@ -4429,7 +4480,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -4438,19 +4489,19 @@
         <v>5</v>
       </c>
       <c r="G123" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H123" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I123" t="s">
-        <v>54</v>
-      </c>
-      <c r="S123" t="s">
-        <v>92</v>
-      </c>
-      <c r="T123" t="s">
-        <v>93</v>
+        <v>58</v>
+      </c>
+      <c r="X123" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="124">
@@ -4461,7 +4512,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -4470,13 +4521,13 @@
         <v>5</v>
       </c>
       <c r="G124" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H124" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I124" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125">
@@ -4487,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4496,13 +4547,13 @@
         <v>10</v>
       </c>
       <c r="G125" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H125" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I125" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="126">
@@ -4513,7 +4564,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4522,13 +4573,13 @@
         <v>25</v>
       </c>
       <c r="G126" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127">
@@ -4539,7 +4590,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -4548,13 +4599,13 @@
         <v>5</v>
       </c>
       <c r="G127" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H127" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I127" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128">
@@ -4565,7 +4616,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -4574,13 +4625,13 @@
         <v>5</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H128" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I128" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="129">
@@ -4591,7 +4642,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -4600,13 +4651,13 @@
         <v>5</v>
       </c>
       <c r="G129" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H129" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I129" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
